--- a/ML-Entrees/ig/StructureDefinition-fr-lm-personne-structure.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-personne-structure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T10:50:27+00:00</t>
+    <t>2026-04-07T13:39:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-personne-structure.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-personne-structure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T13:39:53+00:00</t>
+    <t>2026-04-08T09:43:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-personne-structure.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-personne-structure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T09:43:36+00:00</t>
+    <t>2026-04-08T13:03:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-personne-structure.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-personne-structure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T13:03:38+00:00</t>
+    <t>2026-04-08T14:07:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-personne-structure.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-personne-structure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T14:07:03+00:00</t>
+    <t>2026-04-09T12:24:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-personne-structure.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-personne-structure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T12:24:05+00:00</t>
+    <t>2026-04-13T08:58:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-personne-structure.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-personne-structure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T08:58:24+00:00</t>
+    <t>2026-04-13T09:04:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-personne-structure.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-personne-structure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T09:04:52+00:00</t>
+    <t>2026-04-14T07:59:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-personne-structure.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-personne-structure.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="122">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T07:59:58+00:00</t>
+    <t>2026-04-16T07:11:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -274,11 +274,27 @@
 - obligatoire pour les professionnels et les patients.</t>
   </si>
   <si>
-    <t>fr-lm-personne-structure.personne.professionRole</t>
+    <t>fr-lm-personne-structure.personne.roleFonctionnel</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept
 </t>
+  </si>
+  <si>
+    <t>Rôle fonctionnel</t>
+  </si>
+  <si>
+    <t>fr-lm-personne-structure.personne.dateExecution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>Date de l’exécution</t>
+  </si>
+  <si>
+    <t>fr-lm-personne-structure.personne.professionRole</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -675,7 +691,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ19"/>
+  <dimension ref="A1:AJ21"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="55.89453125" customWidth="true" bestFit="true"/>
@@ -1238,7 +1254,7 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G6" t="s" s="2">
         <v>79</v>
@@ -1253,13 +1269,13 @@
         <v>73</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1313,7 +1329,7 @@
         <v>88</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH6" t="s" s="2">
         <v>79</v>
@@ -1327,10 +1343,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1341,7 +1357,7 @@
         <v>74</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>73</v>
@@ -1353,7 +1369,7 @@
         <v>73</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="L7" t="s" s="2">
         <v>92</v>
@@ -1410,13 +1426,13 @@
         <v>73</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>73</v>
@@ -1441,7 +1457,7 @@
         <v>74</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>73</v>
@@ -1453,13 +1469,13 @@
         <v>73</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="L8" t="s" s="2">
-        <v>95</v>
-      </c>
       <c r="M8" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1516,7 +1532,7 @@
         <v>74</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>73</v>
@@ -1527,10 +1543,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1541,7 +1557,7 @@
         <v>74</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>73</v>
@@ -1553,7 +1569,7 @@
         <v>73</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="L9" t="s" s="2">
         <v>97</v>
@@ -1610,13 +1626,13 @@
         <v>73</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>73</v>
@@ -1638,7 +1654,7 @@
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G10" t="s" s="2">
         <v>75</v>
@@ -1653,13 +1669,13 @@
         <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1713,7 +1729,7 @@
         <v>98</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH10" t="s" s="2">
         <v>75</v>
@@ -1727,10 +1743,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1741,7 +1757,7 @@
         <v>74</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>73</v>
@@ -1753,7 +1769,7 @@
         <v>73</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="L11" t="s" s="2">
         <v>102</v>
@@ -1810,13 +1826,13 @@
         <v>73</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>73</v>
@@ -1838,10 +1854,10 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>73</v>
@@ -1853,7 +1869,7 @@
         <v>73</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="L12" t="s" s="2">
         <v>104</v>
@@ -1913,10 +1929,10 @@
         <v>103</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>73</v>
@@ -1941,7 +1957,7 @@
         <v>74</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>73</v>
@@ -1953,13 +1969,13 @@
         <v>73</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2016,7 +2032,7 @@
         <v>74</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>73</v>
@@ -2027,10 +2043,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2053,13 +2069,13 @@
         <v>73</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2110,7 +2126,7 @@
         <v>73</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>74</v>
@@ -2127,10 +2143,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2153,13 +2169,13 @@
         <v>73</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2210,7 +2226,7 @@
         <v>73</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>74</v>
@@ -2227,10 +2243,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2253,13 +2269,13 @@
         <v>73</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2310,7 +2326,7 @@
         <v>73</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>74</v>
@@ -2327,10 +2343,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2341,7 +2357,7 @@
         <v>74</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>73</v>
@@ -2353,13 +2369,13 @@
         <v>73</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>92</v>
+        <v>115</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>92</v>
+        <v>115</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2410,13 +2426,13 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>73</v>
@@ -2427,10 +2443,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2441,7 +2457,7 @@
         <v>74</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>73</v>
@@ -2453,13 +2469,13 @@
         <v>73</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2510,13 +2526,13 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>73</v>
@@ -2527,10 +2543,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2541,7 +2557,7 @@
         <v>74</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>73</v>
@@ -2553,13 +2569,13 @@
         <v>73</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2610,18 +2626,218 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ19" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E20" s="2"/>
+      <c r="F20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G20" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K20" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q20" s="2"/>
+      <c r="R20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF20" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E21" s="2"/>
+      <c r="F21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K21" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q21" s="2"/>
+      <c r="R21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF21" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AG21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
         <v>73</v>
       </c>
     </row>
